--- a/06_Roteiros_Estatis/Acompanhamento_Analises_PIBICEM.xlsx
+++ b/06_Roteiros_Estatis/Acompanhamento_Analises_PIBICEM.xlsx
@@ -7,19 +7,20 @@
     <sheet state="visible" name="2_Acompanhamento_Analises" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Análises Descritivas" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="Resumo_Testes" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Source References" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="kVsqiMP93GvFPgFHNvVLCD8HO7TRJCBBfLrJDa3cC2A="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="3tURovucPYpBoxFIIy/dS2d9aPeg/FdaV5N8SOy5Ot4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="455">
   <si>
     <t>Nível de análise</t>
   </si>
@@ -934,6 +935,21 @@
 2025_12_15_HeatMap_Teste_X_quadrado_regiao_corrigida_X_grande_area_CAPES_ING.png
 2025_12_15_Barras_Teste_X_quadrado_regiao_corrigida_X_grande_area_CAPES.png
 2025_12_15_HeatMap_Teste_X_quadrado_regiao_corrigida_X_grande_area_CAPES.png</t>
+  </si>
+  <si>
+    <t>Análise Inferencial – Modelagem Multivariada</t>
+  </si>
+  <si>
+    <t>Avaliar o efeito independente de características institucionais, regionais e de desempenho acadêmico sobre a intensidade de participação das instituições no PIBIC-EM</t>
+  </si>
+  <si>
+    <t>Modelo Linear Generalizado (GLM) com distribuição Quasi-Poisson e função de ligação log</t>
+  </si>
+  <si>
+    <t>São pesquisadores que, independentemente de estarem no Norte ou no Sul e independentemente do prestígio (IGC) de sua universidade, conseguiram acumular capital científico individual (produtividade) e estão ancorados em categorias administrativas que lhes oferecem condições materiais de sustentar essa atividade a longo prazo. O PIBIC-EM, portanto, não cria novos pesquisadores 'do zero'; ele oferece uma ferramenta de reprodução para aqueles que já estão engajados na lógica da produção científica e possuem suporte institucional para tal.</t>
+  </si>
+  <si>
+    <t>2026_02_10_modelo_multivariado_3_.pdf</t>
   </si>
   <si>
     <t>Quais instituições retornam sistematicamente ao programa?</t>
@@ -1144,106 +1160,400 @@
 2025_12_18_instituicao_com_maior_numero_de_proponentes_centro_oeste.png</t>
   </si>
   <si>
-    <t>1. A Anatomia da Desigualdade</t>
-  </si>
-  <si>
-    <t>Relação Testada</t>
-  </si>
-  <si>
-    <t>Arquivo Ref.</t>
-  </si>
-  <si>
-    <t>Resultado</t>
-  </si>
-  <si>
-    <t>Interpretação para o Artigo</t>
-  </si>
-  <si>
-    <t>Fidelidade x Região x Categoria Adm</t>
-  </si>
-  <si>
-    <t>2025_12_18...Fidelidade...</t>
-  </si>
-  <si>
-    <t>Associação Forte. A chance de ser um pesquisador "Fiel" (alta recorrência) não é aleatória; ela depende drasticamente da combinação entre onde você está e em que tipo de instituição atua.</t>
-  </si>
-  <si>
-    <t>Crucial: O "leaky pipeline" (vazamento) de orientadores é seletivo. Certas regiões/instituições retêm talentos, outras funcionam apenas como portas giratórias (entra e sai).</t>
-  </si>
-  <si>
-    <t>Região x Grande Área</t>
-  </si>
-  <si>
-    <t>2025_12_15...Grande_Area...</t>
-  </si>
-  <si>
-    <t>Associação Significativa. As áreas do conhecimento não se distribuem igualmente no território.</t>
-  </si>
-  <si>
-    <t>O PIBIC-EM não fomenta a ciência de forma neutra; ele reforça vocações regionais preexistentes ou desigualdades de oferta disciplinar.</t>
-  </si>
-  <si>
-    <t>Tipo de IES x IGC</t>
-  </si>
-  <si>
-    <t>2025_12_09...Tipo_IES_x_IGC</t>
-  </si>
-  <si>
-    <t>Fortíssima Associação (Cramer's V alto). Federais quase sempre têm IGC Alto; Privadas variam mais.</t>
-  </si>
-  <si>
-    <t>Justificativa Metodológica: Não podemos colocar "Tipo de IES" e "IGC" no modelo de regressão sem tratar a colinearidade. Elas medem quase a mesma coisa no setor público.</t>
-  </si>
-  <si>
-    <t>Tipo de IES x Região</t>
-  </si>
-  <si>
-    <t>2025_12_09...Tipo_IES_x_Regiao</t>
-  </si>
-  <si>
-    <t>Associação Significativa. O perfil institucional muda conforme a geografia (ex: o Norte depende mais de Federais/Estaduais; o Sul/Sudeste tem mais presença Privada/Comunitária).</t>
-  </si>
-  <si>
-    <t>A política nacional única (café com leite para todos) ignora que a rede institucional de suporte é heterogênea no território.</t>
-  </si>
-  <si>
-    <t>2. A Dinâmica da Recompensa (Achados de Performance)</t>
-  </si>
-  <si>
-    <t>Variável</t>
-  </si>
-  <si>
-    <t>Resultado Atualizado</t>
-  </si>
-  <si>
-    <t>Interpretação Crítica</t>
-  </si>
-  <si>
-    <t>Região</t>
-  </si>
-  <si>
-    <t>Disparidade Confirmada (p &lt; 0.05). Sul (M=2.09) &gt; Norte (M=1.63).</t>
-  </si>
-  <si>
-    <t>O pesquisador do Sul tem uma "sobrevida" maior no programa. O desenho da política favorece a manutenção de vínculos nessa região.</t>
-  </si>
-  <si>
-    <t>Tipo de IES</t>
-  </si>
-  <si>
-    <t>Tendência (p = 0.079). Privadas (M=2.16) &gt; Federais (M=1.77).</t>
-  </si>
-  <si>
-    <t>Apesar da força estrutural das Federais, o pesquisador da Privada que entra tende a ficar mais. Isso sugere que, para a Privada, o PIBIC-EM pode ser uma estratégia institucional vital de captação de recursos, gerando maior pressão por recorrência.</t>
-  </si>
-  <si>
-    <t>Produção ($h-index$)</t>
-  </si>
-  <si>
-    <t>Não Significativo (p = 0.419).</t>
-  </si>
-  <si>
-    <t>O Achado Contra-Intuitivo: A "elite produtiva" não domina a recorrência. O programa é permeável a diferentes perfis produtivos, mas geograficamente excludente.</t>
+    <t>Variáveis e Características</t>
+  </si>
+  <si>
+    <t>Resultados Estatísticos (Média/Frequência/X²)</t>
+  </si>
+  <si>
+    <t>P-valor e Significância</t>
+  </si>
+  <si>
+    <t>Tamanho do Efeito/Associação (Inferred)</t>
+  </si>
+  <si>
+    <t>Interpretação e Conclusões</t>
+  </si>
+  <si>
+    <t>Fonte</t>
+  </si>
+  <si>
+    <t>Macro (Geral)</t>
+  </si>
+  <si>
+    <t>Distribuição nacional e histórica de bolsas de Iniciação Científica (IC e ICJ)</t>
+  </si>
+  <si>
+    <t>Crescimento de 1.321 (1984) para 27.717 (2015) bolsas de IC; ICJ saltou de 2% (2003) para 28% (2015) do total.</t>
+  </si>
+  <si>
+    <t>Not in source</t>
+  </si>
+  <si>
+    <t>Forte tendência de crescimento e valorização histórica.</t>
+  </si>
+  <si>
+    <t>A Iniciação Científica consolidou-se como estratégia central de Estado para identificação precoce de talentos e redução do tempo de titulação na pós-graduação.</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>Macro (Regional)</t>
+  </si>
+  <si>
+    <t>Concentração de programas e bolsas de IC/PIBIC-EM por Região Geográfica</t>
+  </si>
+  <si>
+    <t>Sudeste (40,5% a 63%); Nordeste (26,5%); Norte (15,5%); Centro-Oeste (11%); Sul (6,5% a 39.995 bolsas).</t>
+  </si>
+  <si>
+    <t>Forte desigualdade regional e concentração de recursos.</t>
+  </si>
+  <si>
+    <t>Há uma predominância histórica das regiões Sul e Sudeste, refletindo desigualdades na infraestrutura de pesquisa e a necessidade de políticas de desconcentração para evitar a "migração de cérebros".</t>
+  </si>
+  <si>
+    <t>2-7</t>
+  </si>
+  <si>
+    <t>Institucional</t>
+  </si>
+  <si>
+    <t>Distribuição da amostra por Categoria Administrativa das IES (PIBIC-EM)</t>
+  </si>
+  <si>
+    <t>Federal: 56,2% a 59,9%; Privada: 20,5% a 21,9%; Estadual: 14,8% a 15,4%; Municipal/Outras: 2,8% a 3,1%.</t>
+  </si>
+  <si>
+    <t>Predomínio absoluto do setor público federal.</t>
+  </si>
+  <si>
+    <t>O programa PIBIC-EM é majoritariamente executado e ancorado em universidades federais, que atuam como eixo estruturante da pesquisa científica nacional.</t>
+  </si>
+  <si>
+    <t>8-10</t>
+  </si>
+  <si>
+    <t>Institucional (Qualidade)</t>
+  </si>
+  <si>
+    <t>Associação entre Tipo de Instituição (IES) e Índice Geral de Cursos (IGC)</t>
+  </si>
+  <si>
+    <t>$X^2(3) = 30,0$  e  $X^2(8) = 482$ . Universidades Federais detêm entre 84,5% e 98,4% do grupo IGC Alto.</t>
+  </si>
+  <si>
+    <t>$p &lt; 0,001$  (Altamente significativo)</t>
+  </si>
+  <si>
+    <t>V de Cramer = 0,243 a 0,667 (Moderado a Muito Forte).</t>
+  </si>
+  <si>
+    <t>Observa-se uma concentração maciça de indicadores de alta qualidade (IGC Alto) em instituições federais, enquanto privadas e municipais associam-se ao IGC Médio.</t>
+  </si>
+  <si>
+    <t>8, 11-15</t>
+  </si>
+  <si>
+    <t>Regional (Diferenciação)</t>
+  </si>
+  <si>
+    <t>Associação entre Categoria Administrativa da IES e Região Geográfica</t>
+  </si>
+  <si>
+    <t>$X^2(16) = 93,4$  e  $X^2(32) = 126$ .</t>
+  </si>
+  <si>
+    <t>V de Cramer = 0,208 a 0,241 (Moderado).</t>
+  </si>
+  <si>
+    <t>Federais são cruciais para a interiorização no Norte/Nordeste; IES privadas concentram-se no Sul/Sudeste. O Sul apresenta super-representação de IES com IGC Alto.</t>
+  </si>
+  <si>
+    <t>12, 16, 17</t>
+  </si>
+  <si>
+    <t>Grande Área</t>
+  </si>
+  <si>
+    <t>Participação e médias de chamadas do PIBIC-EM por Grande Área (CAPES)</t>
+  </si>
+  <si>
+    <t>Engenharias ( $M=2,67$ ); Saúde ( $M=1,96$ ); Biológicas/Exatas ( $M=1,92$ ); Humanas ( $M=1,77$ ). ANOVA:  $F(8, 26,6) = 1,30$ .</t>
+  </si>
+  <si>
+    <t>$p = 0,286$  (Não significativo)</t>
+  </si>
+  <si>
+    <t>$\epsilon^2 = 0,0144$  (Efeito desprezível).</t>
+  </si>
+  <si>
+    <t>A adesão ao programa é homogênea entre as grandes áreas; as diferenças nas médias são explicadas por trajetórias individuais e não por padrões sistêmicos das áreas.</t>
+  </si>
+  <si>
+    <t>8, 18-21</t>
+  </si>
+  <si>
+    <t>Específico (Associação)</t>
+  </si>
+  <si>
+    <t>Associação entre Tipo de IES e Nível de Produção Acadêmica</t>
+  </si>
+  <si>
+    <t>$X^2(8) = 35,1$ .</t>
+  </si>
+  <si>
+    <t>$p &lt; 0,001$  (Significativo)</t>
+  </si>
+  <si>
+    <t>V de Cramer = 0,180 (Pequeno a moderado).</t>
+  </si>
+  <si>
+    <t>Instituições públicas estaduais e institutos de pesquisa tendem a apresentar alta produção; Federais mostram perfil de produção média/baixa na amostra específica.</t>
+  </si>
+  <si>
+    <t>8, 9</t>
+  </si>
+  <si>
+    <t>Específico (Recorrência)</t>
+  </si>
+  <si>
+    <t>Diferença no número de chamadas participadas por Tipo de IES e IGC</t>
+  </si>
+  <si>
+    <t>Média Privada ( $M=2,16$ ) vs Federal ( $M=1,77$ ); IGC Alto ( $M=1,87$ ) vs Médio ( $M=1,86$ ). Welch's  $F = 2,19$ .</t>
+  </si>
+  <si>
+    <t>$p = 0,079$  e  $p = 0,477$  (Não significativo)</t>
+  </si>
+  <si>
+    <t>$r_{rb} = -0,04$  (Inexpressivo).</t>
+  </si>
+  <si>
+    <t>O tipo de gestão institucional ou o nível do IGC não determinam a intensidade de participação (recorrência) do pesquisador no programa.</t>
+  </si>
+  <si>
+    <t>8, 9, 22-26</t>
+  </si>
+  <si>
+    <t>Colinearidade entre Tipo de IES e Natureza Jurídica/Administrativa</t>
+  </si>
+  <si>
+    <t>$X^2(28) = 2164$ .</t>
+  </si>
+  <si>
+    <t>$p &lt; 0,001$  (Significância total)</t>
+  </si>
+  <si>
+    <t>Coeficiente de Contingência = 0,894 (Extremamente alto).</t>
+  </si>
+  <si>
+    <t>Existe uma colinearidade rígida; cada tipo de instituição está estritamente vinculado à sua natureza jurídica, sem casos híbridos significativos.</t>
+  </si>
+  <si>
+    <t>12, 27</t>
+  </si>
+  <si>
+    <t>Validação Estatística</t>
+  </si>
+  <si>
+    <t>Testes de Normalidade e Homogeneidade (Resíduos das Chamadas)</t>
+  </si>
+  <si>
+    <t>Shapiro-Wilk:  $W=0,811$ ; Levene:  $F(8,532)=0,96$ .</t>
+  </si>
+  <si>
+    <t>$W: p &lt; 0,001$ ;  $F: p=0,469$ .</t>
+  </si>
+  <si>
+    <t>Violação da normalidade; homogeneidade preservada.</t>
+  </si>
+  <si>
+    <t>A variância é homogênea, mas a violação da normalidade sugere que a distribuição de bolsas não segue um padrão normal puro, exigindo cautela na ANOVA.</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Evolução Econômica</t>
+  </si>
+  <si>
+    <t>Correlação entre valor das bolsas, salário mínimo e inflação (1996-2015)</t>
+  </si>
+  <si>
+    <t>1996: 4,77 salários; 2015: 3,02 salários. Inflação acumulada: 122,95%.</t>
+  </si>
+  <si>
+    <t>Redução acentuada (Depreciação) do poder de compra.</t>
+  </si>
+  <si>
+    <t>O investimento real diminuiu; a bolsa equivale a cerca de 40% do salário mínimo, o que pode desestimular a entrada de jovens de baixa renda.</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Gestão e Política</t>
+  </si>
+  <si>
+    <t>Execução de metas e fomento (PIBIC-EM/PIBIC-Jr)</t>
+  </si>
+  <si>
+    <t>Crescimento de 377 (2003) para 4.053 (2010) bolsas PIBIC-Jr.</t>
+  </si>
+  <si>
+    <t>Crescimento superior a 1.000%.</t>
+  </si>
+  <si>
+    <t>Consolidação da política de formação inicial, embora haja hiatos entre a formulação estratégica e a implementação tático-operacional no CNPq.</t>
+  </si>
+  <si>
+    <t>3, 28</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Iniciação Científica Júnior desafios à materialização de um círculo virtuoso.pdf</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>A História e os objetivos da Iniciação Científica no Ensino Médio uma análise a partir dos programas do Estado do Rio de Janeiro.pdf</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>A iniciação à pesquisa no Brasil políticas de formação de jovens pesquisadores.pdf</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>A_iniciacao_a_pesquisa_no_Brasil_politicas_de_form.pdf</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Programas de iniciação científica para o ensino médio no Brasil.pdf</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>A iniciação científica no contexto da Educação Básica - Um estudo Baseado na Analálise da Produção Acadêmica.docx</t>
+  </si>
+  <si>
+    <t>iniciacao-cientifica-junior-as-politicas-publicas-de-fomento-a-formacao-de-pesquisadores-na-educacao-basica-brasileira.pdf</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>2025_11_20_participacao_PIBIC-EM_v4.pdf</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2025_11_16_ANOVA_one_way_Numero_de_chamada_Nivel_producao_3grupos.pdf</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2025_11_20_tipoIES_IGC_contingencia.pdf</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2025_12_09_participacao_PIBIC-EM_categoria_adm_corrigida_v4.omv.pdf</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>2025_12_09_Teste_X_quadrado_tipo_ies_corrigido_X_igc_categoria.pdf</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>2025_12_15_Teste_X_quadrado_categoria_adm_corrigida_X_igc_categoria.pdf</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2025_12_09_Teste_X_quadrado_categoria_adm_corrigida_X_Regiao_corrigida.pdf</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2025_12_13_Teste_X_quadrado_regiao_corrigida_X_igc_categoria.pdf</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2025_11_16_grande_area_de_conhecimento_CAPES_participacao_PIBIC-EM.pdf</t>
+  </si>
+  <si>
+    <t>2025_11_16_ANOVA_grande_area_de_conhecimento_CAPES_participacao_PIBIC-EM.pdf</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>2025_11_16_Kruskal_Vallis_no_parametric_ANOVA_Numero_de_chamada_Nivel_producao_3grupos.pdf</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>2025_11_14_ANOVA_one_way_Numero_de_chamada_tipo_de_Instituicao.pdf</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Planejamento e gestão estratégica- o caso do CNPq.pdf</t>
   </si>
 </sst>
 </file>
@@ -1357,12 +1667,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF1F1F1F"/>
-      <name val="&quot;Google Sans Text&quot;"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF444746"/>
-      <name val="&quot;Google Sans Text&quot;"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1486,7 +1796,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1574,6 +1884,9 @@
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -1594,10 +1907,25 @@
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1620,6 +1948,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -10111,11 +10443,58 @@
         <v>46006.0</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="26">
+        <v>45698.0</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="K33" s="16"/>
+    </row>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+    </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -10123,14 +10502,14 @@
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="D44" s="16"/>
@@ -10330,24 +10709,24 @@
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="30"/>
+      <c r="A79" s="31"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="31" t="s">
-        <v>259</v>
+      <c r="A80" s="32" t="s">
+        <v>264</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
@@ -11315,12 +11694,13 @@
     <hyperlink r:id="rId53" ref="J30"/>
     <hyperlink r:id="rId54" ref="B31"/>
     <hyperlink r:id="rId55" ref="J31"/>
-    <hyperlink r:id="rId56" ref="C80"/>
+    <hyperlink r:id="rId56" ref="J33"/>
+    <hyperlink r:id="rId57" ref="C80"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId57"/>
+  <drawing r:id="rId58"/>
 </worksheet>
 </file>
 
@@ -11344,39 +11724,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="H1" s="32" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33" t="s">
         <v>268</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="E1" s="33" t="s">
         <v>270</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="F1" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="G1" s="33" t="s">
         <v>272</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>275</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>277</v>
       </c>
       <c r="M1" s="16"/>
     </row>
@@ -11384,15 +11764,15 @@
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25" t="s">
-        <v>273</v>
-      </c>
-      <c r="M2" s="32"/>
+        <v>278</v>
+      </c>
+      <c r="M2" s="33"/>
     </row>
     <row r="3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33" t="s">
-        <v>274</v>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="4">
@@ -11400,47 +11780,47 @@
         <v>46007.0</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33" t="s">
-        <v>287</v>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="6">
@@ -11448,47 +11828,47 @@
         <v>46007.0</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33" t="s">
-        <v>298</v>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="8">
@@ -11496,45 +11876,45 @@
         <v>46007.0</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="s">
-        <v>308</v>
+      <c r="A9" s="34" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -11542,40 +11922,45 @@
         <v>46007.0</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>317</v>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21">
+        <v>45698.0</v>
       </c>
     </row>
   </sheetData>
@@ -11607,155 +11992,568 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.43"/>
-    <col customWidth="1" min="2" max="2" width="41.43"/>
-    <col customWidth="1" min="3" max="3" width="60.57"/>
-    <col customWidth="1" min="4" max="4" width="74.43"/>
-    <col customWidth="1" min="5" max="5" width="56.71"/>
+    <col customWidth="1" min="1" max="1" width="24.14"/>
+    <col customWidth="1" min="2" max="2" width="40.57"/>
+    <col customWidth="1" min="3" max="3" width="44.43"/>
+    <col customWidth="1" min="4" max="4" width="38.57"/>
+    <col customWidth="1" min="5" max="5" width="30.71"/>
+    <col customWidth="1" min="6" max="6" width="42.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="s">
-        <v>318</v>
-      </c>
-      <c r="E1" s="35"/>
+      <c r="A1" s="35"/>
+      <c r="E1" s="36"/>
     </row>
     <row r="2">
-      <c r="A2" s="35" t="s">
-        <v>319</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="D2" s="35" t="s">
-        <v>322</v>
-      </c>
-      <c r="E2" s="35"/>
+      <c r="A2" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>326</v>
-      </c>
-      <c r="E3" s="35"/>
+      <c r="A3" s="39" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>332</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="E4" s="35"/>
+      <c r="A4" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>332</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>339</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="B5" s="37" t="s">
+      <c r="A5" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>343</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" s="39" t="s">
         <v>332</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="39" t="s">
+        <v>345</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>346</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="s">
-        <v>335</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>337</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>338</v>
-      </c>
-      <c r="E6" s="35"/>
+      <c r="A6" s="39" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>351</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>352</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>353</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="36"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="35"/>
+      <c r="A7" s="39" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>359</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="s">
+        <v>361</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>364</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>365</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>366</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>339</v>
+      <c r="A9" s="40" t="s">
+        <v>368</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>369</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>370</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>372</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>373</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>342</v>
+      <c r="A10" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>378</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>379</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>380</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="s">
-        <v>343</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>344</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>345</v>
+      <c r="A11" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>384</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>385</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>386</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="s">
-        <v>346</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>347</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>348</v>
+      <c r="A12" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>391</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>392</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>393</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="s">
-        <v>349</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>350</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>351</v>
+      <c r="A13" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>397</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>332</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>403</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>332</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>404</v>
+      </c>
+      <c r="F14" s="40" t="s">
+        <v>405</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="6.29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="s">
+        <v>407</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="43" t="s">
+        <v>413</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="s">
+        <v>417</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="s">
+        <v>419</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="s">
+        <v>427</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="s">
+        <v>429</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="s">
+        <v>431</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="s">
+        <v>432</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="s">
+        <v>434</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="s">
+        <v>436</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="s">
+        <v>438</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="s">
+        <v>440</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="s">
+        <v>443</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="s">
+        <v>447</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="s">
+        <v>449</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="s">
+        <v>450</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="s">
+        <v>451</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="s">
+        <v>452</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="s">
+        <v>453</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>454</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/06_Roteiros_Estatis/Acompanhamento_Analises_PIBICEM.xlsx
+++ b/06_Roteiros_Estatis/Acompanhamento_Analises_PIBICEM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="457">
   <si>
     <t>Nível de análise</t>
   </si>
@@ -950,6 +950,12 @@
   </si>
   <si>
     <t>2026_02_10_modelo_multivariado_3_.pdf</t>
+  </si>
+  <si>
+    <t>Avaliar o efeito da participação no PIBIC-EM entre pesquisadores dos IF/CEFETs e das Universidades Federais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os resultados deste modelo específico (tabela \ref{tab:poisson-federal}) corroboram a tendência observada: mantendo constante a produtividade acadêmica, os docentes dos Institutos Federais apresentam uma probabilidade de participação 15% superior à de seus pares nas Universidades Federais ($IRR=1{,}15$; $IC~95\%: 1{,}01\text{--}1{,}31$; $p=0{,}033$). </t>
   </si>
   <si>
     <t>Quais instituições retornam sistematicamente ao programa?</t>
@@ -9259,7 +9265,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.29"/>
+    <col customWidth="1" min="1" max="1" width="20.0"/>
     <col customWidth="1" min="2" max="2" width="27.29"/>
     <col customWidth="1" min="3" max="3" width="26.0"/>
     <col customWidth="1" min="4" max="4" width="29.14"/>
@@ -10457,9 +10463,6 @@
       <c r="K32" s="16"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="26">
-        <v>45698.0</v>
-      </c>
       <c r="B33" s="26"/>
       <c r="C33" s="14" t="s">
         <v>259</v>
@@ -10479,9 +10482,32 @@
       <c r="J33" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="K33" s="16"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1"/>
+      <c r="K33" s="26">
+        <v>45698.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="B34" s="16"/>
+      <c r="C34" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="J34" s="16"/>
+      <c r="K34" s="26">
+        <v>45700.0</v>
+      </c>
+    </row>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="29"/>
@@ -10715,18 +10741,18 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="32" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
@@ -11729,34 +11755,34 @@
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G1" s="33" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I1" s="33" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J1" s="33" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K1" s="33" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L1" s="33" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M1" s="16"/>
     </row>
@@ -11764,7 +11790,7 @@
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M2" s="33"/>
     </row>
@@ -11772,7 +11798,7 @@
       <c r="A3" s="34"/>
       <c r="B3" s="34"/>
       <c r="C3" s="34" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -11780,47 +11806,47 @@
         <v>46007.0</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="34" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6">
@@ -11828,47 +11854,47 @@
         <v>46007.0</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="34"/>
       <c r="B7" s="34"/>
       <c r="C7" s="34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8">
@@ -11876,45 +11902,45 @@
         <v>46007.0</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="34" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -11922,40 +11948,40 @@
         <v>46007.0</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12">
@@ -12009,298 +12035,298 @@
         <v>42</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="39" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G3" s="41" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="39" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G4" s="41" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="39" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="39" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="39" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G7" s="41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="40" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G8" s="40" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="40" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E9" s="40" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="39" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="39" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G11" s="41" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="39" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="39" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G13" s="41" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="40" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -12323,87 +12349,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="42" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="43" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="43" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="43" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="43" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="43" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="43" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>58</v>
@@ -12411,119 +12437,119 @@
     </row>
     <row r="12">
       <c r="A12" s="43" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B17" s="42" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="43" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="43" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="43" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="43" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="43" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="43" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="43" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B26" s="42" t="s">
         <v>191</v>
@@ -12531,7 +12557,7 @@
     </row>
     <row r="27">
       <c r="A27" s="43" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B27" s="42" t="s">
         <v>184</v>
@@ -12539,7 +12565,7 @@
     </row>
     <row r="28">
       <c r="A28" s="43" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B28" s="42" t="s">
         <v>207</v>
@@ -12547,10 +12573,10 @@
     </row>
     <row r="29">
       <c r="A29" s="43" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/06_Roteiros_Estatis/Acompanhamento_Analises_PIBICEM.xlsx
+++ b/06_Roteiros_Estatis/Acompanhamento_Analises_PIBICEM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="458">
   <si>
     <t>Nível de análise</t>
   </si>
@@ -956,6 +956,9 @@
   </si>
   <si>
     <t xml:space="preserve">Os resultados deste modelo específico (tabela \ref{tab:poisson-federal}) corroboram a tendência observada: mantendo constante a produtividade acadêmica, os docentes dos Institutos Federais apresentam uma probabilidade de participação 15% superior à de seus pares nas Universidades Federais ($IRR=1{,}15$; $IC~95\%: 1{,}01\text{--}1{,}31$; $p=0{,}033$). </t>
+  </si>
+  <si>
+    <t>2026_02_12_modelo_multivariado_3_universidade_federal_IFs.pdf</t>
   </si>
   <si>
     <t>Quais instituições retornam sistematicamente ao programa?</t>
@@ -10503,7 +10506,9 @@
       <c r="I34" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="J34" s="16"/>
+      <c r="J34" s="19" t="s">
+        <v>266</v>
+      </c>
       <c r="K34" s="26">
         <v>45700.0</v>
       </c>
@@ -10741,18 +10746,18 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
@@ -11721,12 +11726,13 @@
     <hyperlink r:id="rId54" ref="B31"/>
     <hyperlink r:id="rId55" ref="J31"/>
     <hyperlink r:id="rId56" ref="J33"/>
-    <hyperlink r:id="rId57" ref="C80"/>
+    <hyperlink r:id="rId57" ref="J34"/>
+    <hyperlink r:id="rId58" ref="C80"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId58"/>
+  <drawing r:id="rId59"/>
 </worksheet>
 </file>
 
@@ -11755,34 +11761,34 @@
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G1" s="33" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I1" s="33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J1" s="33" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K1" s="33" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L1" s="33" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M1" s="16"/>
     </row>
@@ -11790,7 +11796,7 @@
       <c r="A2" s="25"/>
       <c r="B2" s="25"/>
       <c r="C2" s="25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M2" s="33"/>
     </row>
@@ -11798,7 +11804,7 @@
       <c r="A3" s="34"/>
       <c r="B3" s="34"/>
       <c r="C3" s="34" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -11806,47 +11812,47 @@
         <v>46007.0</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6">
@@ -11854,47 +11860,47 @@
         <v>46007.0</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="34"/>
       <c r="B7" s="34"/>
       <c r="C7" s="34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8">
@@ -11902,45 +11908,45 @@
         <v>46007.0</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -11948,40 +11954,40 @@
         <v>46007.0</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12">
@@ -12035,298 +12041,298 @@
         <v>42</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="39" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G3" s="41" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="39" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G4" s="41" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="39" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="39" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="39" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G7" s="41" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="40" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G8" s="40" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="40" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E9" s="40" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="39" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="39" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G11" s="41" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="39" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G13" s="41" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="40" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -12349,87 +12355,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="42" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="43" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="43" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="43" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="43" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="43" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="43" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="43" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>58</v>
@@ -12437,119 +12443,119 @@
     </row>
     <row r="12">
       <c r="A12" s="43" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B17" s="42" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="43" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="43" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="B21" s="42" t="s">
         <v>445</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="43" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="43" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="43" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="43" t="s">
+        <v>452</v>
+      </c>
+      <c r="B25" s="42" t="s">
         <v>451</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="43" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B26" s="42" t="s">
         <v>191</v>
@@ -12557,7 +12563,7 @@
     </row>
     <row r="27">
       <c r="A27" s="43" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B27" s="42" t="s">
         <v>184</v>
@@ -12565,7 +12571,7 @@
     </row>
     <row r="28">
       <c r="A28" s="43" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B28" s="42" t="s">
         <v>207</v>
@@ -12573,10 +12579,10 @@
     </row>
     <row r="29">
       <c r="A29" s="43" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>

--- a/06_Roteiros_Estatis/Acompanhamento_Analises_PIBICEM.xlsx
+++ b/06_Roteiros_Estatis/Acompanhamento_Analises_PIBICEM.xlsx
@@ -4,23 +4,24 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="1_Estrutura_Conceitual" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="2_Acompanhamento_Analises" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Análises Descritivas" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Resumo_Testes" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Source References" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Modelo Multivariado Hierárquico" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="2_Acompanhamento_Analises" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Análises Descritivas" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Resumo_Testes" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Source References" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="3tURovucPYpBoxFIIy/dS2d9aPeg/FdaV5N8SOy5Ot4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="WeYdJuOOW23AFINBXDh1N4CQ3jGQ1bqUJbT7/tHgMqQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="611">
   <si>
     <t>Nível de análise</t>
   </si>
@@ -142,6 +143,503 @@
     <t>Etapa 5 – Análise de tendência científica</t>
   </si>
   <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Banco de dados</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>Análise</t>
+  </si>
+  <si>
+    <t>Unidade de análise</t>
+  </si>
+  <si>
+    <t>Variáveis</t>
+  </si>
+  <si>
+    <t>Técnica</t>
+  </si>
+  <si>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>Procedimento analítico</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>Critério de classificação</t>
+  </si>
+  <si>
+    <t>Observação metodológica</t>
+  </si>
+  <si>
+    <t>Arquivos</t>
+  </si>
+  <si>
+    <t>2026_02_24_participacao_PIBIC-EM_categoria_adm_corrigida_v6.csv</t>
+  </si>
+  <si>
+    <t>Análise Inferencial Multivariada – Modelagem Hierárquica (Passo 1)</t>
+  </si>
+  <si>
+    <t>Avaliação do Efeito Institucional Bruto na fidelização ao programa.</t>
+  </si>
+  <si>
+    <t>Pesquisador proponente</t>
+  </si>
+  <si>
+    <t>VD: num_chamadas_participou
+VI: categoria_adm_corrigida</t>
+  </si>
+  <si>
+    <t>Regressão Linear Generalizada (GAMLj) – Quasi-Poisson (função log)</t>
+  </si>
+  <si>
+    <t>Mensurar a disparidade primária na taxa de recorrência em chamadas puramente pela natureza jurídica/administrativa da instituição.</t>
+  </si>
+  <si>
+    <t>Inserção exclusiva da variável institucional como fator preditor principal, sem controles adicionais.</t>
+  </si>
+  <si>
+    <t>2026_02_24_Model_1_foco_institucional_bruto.pdf</t>
+  </si>
+  <si>
+    <t>Ref: Universidade Federal.
+Níveis: p &lt; .05, p &lt; .01, p &lt; .001.</t>
+  </si>
+  <si>
+    <t>Aplicação prévia de filtro de análise de casos completos (h_index &gt;= 0), estabilizando amostra em N=496 para garantir comparabilidade transversal.</t>
+  </si>
+  <si>
+    <t>Análise Inferencial Multivariada – Modelagem Hierárquica (Passo 2)</t>
+  </si>
+  <si>
+    <t>Controle das desigualdades geográficas.</t>
+  </si>
+  <si>
+    <t>VD: num_chamadas_participou
+VIs: categoria_adm_corrigida, regiao_corrigida</t>
+  </si>
+  <si>
+    <t>Avaliar se a disparidade institucional observada no Modelo 1 sofre atenuação ao isolar matematicamente o peso da concentração histórica de recursos.</t>
+  </si>
+  <si>
+    <t>Adição da variável de região geográfica aos fatores principais, mantendo a amostra restrita (N=496).</t>
+  </si>
+  <si>
+    <t>2026_02_24_Model_II_foco_institucional_bruto_controle_geografico.pdf</t>
+  </si>
+  <si>
+    <t>Ref: Universidade Federal e Sudeste.</t>
+  </si>
+  <si>
+    <t>O modelo não incluiu termos de interação territorial (evitando overfitting), focando estritamente nos efeitos principais.</t>
+  </si>
+  <si>
+    <t>Análise Inferencial Multivariada – Modelagem Hierárquica (Passo 3)</t>
+  </si>
+  <si>
+    <t>Controle da capacidade instalada (Infraestrutura/Qualidade).</t>
+  </si>
+  <si>
+    <t>VD: num_chamadas_participou
+VIs: categoria_adm_corrigida, regiao_corrigida, igc_categoria</t>
+  </si>
+  <si>
+    <t>Controlar a influência da infraestrutura e excelência (IGC) na probabilidade de fidelização do pesquisador ao edital.</t>
+  </si>
+  <si>
+    <t>Inserção do indicador de qualidade institucional ao bloco de preditores, mantendo os parâmetros logarítmicos.</t>
+  </si>
+  <si>
+    <t>2026_02_24_Model_III_foco_institucional_bruto_controle_geografico_controle_IGC_.pdf</t>
+  </si>
+  <si>
+    <t>Ref: Universidade Federal, Sudeste e IGC Alto.</t>
+  </si>
+  <si>
+    <t>O valor p da categoria administrativa demonstra que o nivelamento pela infraestrutura contribui para esbater a desvantagem de instituições não-hegemônicas.</t>
+  </si>
+  <si>
+    <t>Análise Inferencial Multivariada – Modelagem Hierárquica (Passo 4)</t>
+  </si>
+  <si>
+    <t>Controle do capital científico individual (Efeito Mateus).</t>
+  </si>
+  <si>
+    <t>VD: num_chamadas_participou
+VIs: categoria_adm_corrigida, regiao_corrigida, igc_categoria, h_index</t>
+  </si>
+  <si>
+    <t>Determinar o peso estrutural do prestígio bibliométrico (Índice H) sobre a recorrência, testando efeitos de supressão nas variáveis institucionais.</t>
+  </si>
+  <si>
+    <t>Inclusão do Índice H do pesquisador como covariável final no modelo hierárquico.</t>
+  </si>
+  <si>
+    <t>2026_02_24_Model_IV_foco_institucional_bruto_controle_geografico_controle_IGC_controle_h_index.pdf</t>
+  </si>
+  <si>
+    <t>Foco na Razão de Taxa de Incidência (IRR / exp(B)).</t>
+  </si>
+  <si>
+    <t>Modelo consolida a inversão analítica: ao equiparar o capital científico, pesquisadores de IFs e Privadas apresentam taxas de fidelização superiores às das Federais.</t>
+  </si>
+  <si>
+    <t>Aqui está a tabela formatada segundo as diretrizes da 7ª edição do manual da APA, consolidando os resultados dos quatro modelos log-lineares (Quasi-Poisson) apresentados nos documentos.</t>
+  </si>
+  <si>
+    <t>Tabela 1</t>
+  </si>
+  <si>
+    <t>Resultados dos Modelos Lineares Generalizados (Quasi-Poisson) para o Número de Chamadas com Participação</t>
+  </si>
+  <si>
+    <t>Preditor</t>
+  </si>
+  <si>
+    <t>Modelo I</t>
+  </si>
+  <si>
+    <t>Modelo II</t>
+  </si>
+  <si>
+    <t>Modelo III</t>
+  </si>
+  <si>
+    <t>Modelo IV</t>
+  </si>
+  <si>
+    <t>Intercepto</t>
+  </si>
+  <si>
+    <t>0.649*** (0.036)</t>
+  </si>
+  <si>
+    <t>0.612*** (0.041)</t>
+  </si>
+  <si>
+    <t>0.449** (0.148)</t>
+  </si>
+  <si>
+    <t>0.461** (0.147)</t>
+  </si>
+  <si>
+    <t>Categoria Administrativa (Ref.: Universidade Federal)</t>
+  </si>
+  <si>
+    <t>Especial</t>
+  </si>
+  <si>
+    <t>0.003 (0.158)</t>
+  </si>
+  <si>
+    <t>-0.030 (0.160)</t>
+  </si>
+  <si>
+    <t>-0.004 (0.167)</t>
+  </si>
+  <si>
+    <t>0.048 (0.168)</t>
+  </si>
+  <si>
+    <t>IF/CEFET</t>
+  </si>
+  <si>
+    <t>0.094 (0.066)</t>
+  </si>
+  <si>
+    <t>0.105 (0.067)</t>
+  </si>
+  <si>
+    <t>0.115 (0.071)</t>
+  </si>
+  <si>
+    <t>0.167* (0.075)</t>
+  </si>
+  <si>
+    <t>Privada com fins lucrativos</t>
+  </si>
+  <si>
+    <t>0.270* (0.117)</t>
+  </si>
+  <si>
+    <t>0.261* (0.118)</t>
+  </si>
+  <si>
+    <t>0.290* (0.130)</t>
+  </si>
+  <si>
+    <t>0.345** (0.132)</t>
+  </si>
+  <si>
+    <t>Privada sem fins lucrativos</t>
+  </si>
+  <si>
+    <t>0.236*** (0.069)</t>
+  </si>
+  <si>
+    <t>0.193** (0.074)</t>
+  </si>
+  <si>
+    <t>0.209** (0.079)</t>
+  </si>
+  <si>
+    <t>0.246** (0.081)</t>
+  </si>
+  <si>
+    <t>Pública Estadual</t>
+  </si>
+  <si>
+    <t>0.078 (0.075)</t>
+  </si>
+  <si>
+    <t>0.057 (0.075)</t>
+  </si>
+  <si>
+    <t>0.076 (0.078)</t>
+  </si>
+  <si>
+    <t>0.079 (0.077)</t>
+  </si>
+  <si>
+    <t>Região Geográfica (Ref.: Sudeste)</t>
+  </si>
+  <si>
+    <t>Centro-Oeste</t>
+  </si>
+  <si>
+    <t>-0.144 (0.097)</t>
+  </si>
+  <si>
+    <t>-0.131 (0.100)</t>
+  </si>
+  <si>
+    <t>-0.110 (0.100)</t>
+  </si>
+  <si>
+    <t>Nordeste</t>
+  </si>
+  <si>
+    <t>0.016 (0.068)</t>
+  </si>
+  <si>
+    <t>0.019 (0.068)</t>
+  </si>
+  <si>
+    <t>0.044 (0.069)</t>
+  </si>
+  <si>
+    <t>Norte</t>
+  </si>
+  <si>
+    <t>-0.114 (0.093)</t>
+  </si>
+  <si>
+    <t>-0.077 (0.098)</t>
+  </si>
+  <si>
+    <t>-0.031 (0.100)</t>
+  </si>
+  <si>
+    <t>Sul</t>
+  </si>
+  <si>
+    <t>0.075 (0.065)</t>
+  </si>
+  <si>
+    <t>0.069 (0.066)</t>
+  </si>
+  <si>
+    <t>0.076 (0.066)</t>
+  </si>
+  <si>
+    <t>Categoria IGC (Ref.: IGC Alto)</t>
+  </si>
+  <si>
+    <t>IGC Médio</t>
+  </si>
+  <si>
+    <t>-0.036 (0.072)</t>
+  </si>
+  <si>
+    <t>-0.045 (0.072)</t>
+  </si>
+  <si>
+    <t>Sem IGC</t>
+  </si>
+  <si>
+    <t>-0.517 (0.439)</t>
+  </si>
+  <si>
+    <t>-0.522 (0.437)</t>
+  </si>
+  <si>
+    <t>Índice H</t>
+  </si>
+  <si>
+    <t>Índice H (centrado)</t>
+  </si>
+  <si>
+    <t>0.004* (0.002)</t>
+  </si>
+  <si>
+    <t>Estatísticas de Ajuste</t>
+  </si>
+  <si>
+    <t>Tamanho da Amostra ($N$)</t>
+  </si>
+  <si>
+    <t>Deviance</t>
+  </si>
+  <si>
+    <t>$R^2$</t>
+  </si>
+  <si>
+    <t>$R^2$ Ajustado</t>
+  </si>
+  <si>
+    <t>Graus de Liberdade Residuais</t>
+  </si>
+  <si>
+    <t>Nota. Os valores representam as estimativas dos coeficientes (Estimates) na escala de $\log(y)$, com os respectivos erros padrão (SE) entre parênteses. Os dados originais foram extraídos dos resultados do Modelo I, Modelo II, Modelo III e Modelo IV. *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
+  </si>
+  <si>
+    <t>Abaixo está a tabela reestruturada de acordo com o padrão APA 7, com os valores dos erros padrões (SE) posicionados imediatamente abaixo das estimativas dos coeficientes.</t>
+  </si>
+  <si>
+    <t>0.649***(0.036)</t>
+  </si>
+  <si>
+    <t>0.612***(0.041)</t>
+  </si>
+  <si>
+    <t>0.449**(0.148)</t>
+  </si>
+  <si>
+    <t>0.461**(0.147)</t>
+  </si>
+  <si>
+    <t>0.003(0.158)</t>
+  </si>
+  <si>
+    <t>-0.030(0.160)</t>
+  </si>
+  <si>
+    <t>-0.004(0.167)</t>
+  </si>
+  <si>
+    <t>0.048(0.168)</t>
+  </si>
+  <si>
+    <t>0.094(0.066)</t>
+  </si>
+  <si>
+    <t>0.105(0.067)</t>
+  </si>
+  <si>
+    <t>0.115(0.071)</t>
+  </si>
+  <si>
+    <t>0.167*(0.075)</t>
+  </si>
+  <si>
+    <t>0.270*(0.117)</t>
+  </si>
+  <si>
+    <t>0.261*(0.118)</t>
+  </si>
+  <si>
+    <t>0.290*(0.130)</t>
+  </si>
+  <si>
+    <t>0.345**(0.132)</t>
+  </si>
+  <si>
+    <t>0.236***(0.069)</t>
+  </si>
+  <si>
+    <t>0.193**(0.074)</t>
+  </si>
+  <si>
+    <t>0.209**(0.079)</t>
+  </si>
+  <si>
+    <t>0.246**(0.081)</t>
+  </si>
+  <si>
+    <t>0.078(0.075)</t>
+  </si>
+  <si>
+    <t>0.057(0.075)</t>
+  </si>
+  <si>
+    <t>0.076(0.078)</t>
+  </si>
+  <si>
+    <t>0.079(0.077)</t>
+  </si>
+  <si>
+    <t>-0.144(0.097)</t>
+  </si>
+  <si>
+    <t>-0.131(0.100)</t>
+  </si>
+  <si>
+    <t>-0.110(0.100)</t>
+  </si>
+  <si>
+    <t>0.016(0.068)</t>
+  </si>
+  <si>
+    <t>0.019(0.068)</t>
+  </si>
+  <si>
+    <t>0.044(0.069)</t>
+  </si>
+  <si>
+    <t>-0.114(0.093)</t>
+  </si>
+  <si>
+    <t>-0.077(0.098)</t>
+  </si>
+  <si>
+    <t>-0.031(0.100)</t>
+  </si>
+  <si>
+    <t>0.075(0.065)</t>
+  </si>
+  <si>
+    <t>0.069(0.066)</t>
+  </si>
+  <si>
+    <t>0.076(0.066)</t>
+  </si>
+  <si>
+    <t>-0.036(0.072)</t>
+  </si>
+  <si>
+    <t>-0.045(0.072)</t>
+  </si>
+  <si>
+    <t>-0.517(0.439)</t>
+  </si>
+  <si>
+    <t>-0.522(0.437)</t>
+  </si>
+  <si>
+    <t>0.004*(0.002)</t>
+  </si>
+  <si>
+    <t>Nota. Os valores representam as estimativas dos coeficientes (Estimates) na escala de $\log(y)$, com os respectivos erros padrão (SE) apresentados entre parênteses logo abaixo de cada coeficiente. Os dados originais foram extraídos dos resultados do Modelo I, Modelo II, Modelo III e Modelo IV. *p &lt; .05. **p &lt; .01. ***p &lt; .001.</t>
+  </si>
+  <si>
     <t>Nº</t>
   </si>
   <si>
@@ -170,9 +668,6 @@
   </si>
   <si>
     <t>Exportações Geradas</t>
-  </si>
-  <si>
-    <t>Data</t>
   </si>
   <si>
     <t>02_2025_11_14_TESTES_ASSOCIACAO_V2.omv</t>
@@ -971,36 +1466,6 @@
   </si>
   <si>
     <t>2025_12_13_Teste_X_quadrado_regiao_corrigida_X_igc_categoria</t>
-  </si>
-  <si>
-    <t>Etapa</t>
-  </si>
-  <si>
-    <t>Análise</t>
-  </si>
-  <si>
-    <t>Unidade de análise</t>
-  </si>
-  <si>
-    <t>Variáveis</t>
-  </si>
-  <si>
-    <t>Técnica</t>
-  </si>
-  <si>
-    <t>Objetivo</t>
-  </si>
-  <si>
-    <t>Procedimento analítico</t>
-  </si>
-  <si>
-    <t>Produto</t>
-  </si>
-  <si>
-    <t>Critério de classificação</t>
-  </si>
-  <si>
-    <t>Observação metodológica</t>
   </si>
   <si>
     <t>Análise Descritiva Institucional</t>
@@ -1598,19 +2063,10 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="12.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -1628,6 +2084,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1636,12 +2111,6 @@
     <font>
       <u/>
       <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <u/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1669,10 +2138,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF1F1F1F"/>
-      <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
       <b/>
@@ -1805,7 +2270,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1824,10 +2289,34 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1842,7 +2331,7 @@
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1857,63 +2346,54 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -1961,6 +2441,10 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -9264,6 +9748,974 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="31.43"/>
+    <col customWidth="1" min="3" max="3" width="39.57"/>
+    <col customWidth="1" min="4" max="4" width="39.86"/>
+    <col customWidth="1" min="5" max="5" width="24.43"/>
+    <col customWidth="1" min="6" max="6" width="28.57"/>
+    <col customWidth="1" min="7" max="7" width="37.29"/>
+    <col customWidth="1" min="8" max="8" width="41.86"/>
+    <col customWidth="1" min="9" max="9" width="48.57"/>
+    <col customWidth="1" min="10" max="10" width="38.57"/>
+    <col customWidth="1" min="11" max="11" width="34.86"/>
+    <col customWidth="1" min="12" max="12" width="48.29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8">
+        <v>46077.0</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8">
+        <v>46077.0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8">
+        <v>46077.0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8">
+        <v>46077.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="11">
+        <v>496.0</v>
+      </c>
+      <c r="C44" s="11">
+        <v>496.0</v>
+      </c>
+      <c r="D44" s="11">
+        <v>496.0</v>
+      </c>
+      <c r="E44" s="11">
+        <v>496.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="13">
+        <v>239143.0</v>
+      </c>
+      <c r="C45" s="13">
+        <v>235383.0</v>
+      </c>
+      <c r="D45" s="13">
+        <v>234409.0</v>
+      </c>
+      <c r="E45" s="13">
+        <v>232068.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" s="13">
+        <v>32.0</v>
+      </c>
+      <c r="C46" s="13">
+        <v>48.0</v>
+      </c>
+      <c r="D46" s="13">
+        <v>52.0</v>
+      </c>
+      <c r="E46" s="13">
+        <v>61.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="C47" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="D47" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="E47" s="13">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B48" s="11">
+        <v>490.0</v>
+      </c>
+      <c r="C48" s="11">
+        <v>486.0</v>
+      </c>
+      <c r="D48" s="11">
+        <v>484.0</v>
+      </c>
+      <c r="E48" s="11">
+        <v>483.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" s="12"/>
+      <c r="C74" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B75" s="12"/>
+      <c r="C75" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" s="12"/>
+      <c r="C76" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B77" s="12"/>
+      <c r="C77" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B84" s="11">
+        <v>496.0</v>
+      </c>
+      <c r="C84" s="11">
+        <v>496.0</v>
+      </c>
+      <c r="D84" s="11">
+        <v>496.0</v>
+      </c>
+      <c r="E84" s="11">
+        <v>496.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B85" s="13">
+        <v>239143.0</v>
+      </c>
+      <c r="C85" s="13">
+        <v>235383.0</v>
+      </c>
+      <c r="D85" s="13">
+        <v>234409.0</v>
+      </c>
+      <c r="E85" s="13">
+        <v>232068.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B86" s="13">
+        <v>32.0</v>
+      </c>
+      <c r="C86" s="13">
+        <v>48.0</v>
+      </c>
+      <c r="D86" s="13">
+        <v>52.0</v>
+      </c>
+      <c r="E86" s="13">
+        <v>61.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B87" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="C87" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="D87" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="E87" s="13">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B88" s="11">
+        <v>490.0</v>
+      </c>
+      <c r="C88" s="11">
+        <v>486.0</v>
+      </c>
+      <c r="D88" s="11">
+        <v>484.0</v>
+      </c>
+      <c r="E88" s="11">
+        <v>483.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="M2"/>
+    <hyperlink r:id="rId2" ref="M3"/>
+    <hyperlink r:id="rId3" ref="M4"/>
+    <hyperlink r:id="rId4" ref="M5"/>
+  </hyperlinks>
+  <drawing r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
@@ -9283,1248 +10735,1248 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.0" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="11">
+      <c r="A2" s="19">
         <v>1.0</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" s="13">
+      <c r="B2" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="K2" s="21">
         <v>45974.0</v>
       </c>
     </row>
     <row r="3" ht="57.75" customHeight="1">
-      <c r="A3" s="14">
+      <c r="A3" s="22">
         <v>2.0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="15">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="I3" s="22"/>
+      <c r="J3" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="K3" s="23">
         <v>45974.0</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="16"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
     </row>
     <row r="4" ht="70.5" customHeight="1">
-      <c r="A4" s="14">
+      <c r="A4" s="22">
         <v>3.0</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="15">
+      <c r="B4" s="22"/>
+      <c r="C4" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="I4" s="22"/>
+      <c r="J4" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="K4" s="23">
         <v>45974.0</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="16"/>
-      <c r="AA4" s="16"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
     </row>
     <row r="5" ht="69.0" customHeight="1">
-      <c r="A5" s="14">
+      <c r="A5" s="22">
         <v>4.0</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="15">
+      <c r="B5" s="22"/>
+      <c r="C5" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="I5" s="22"/>
+      <c r="J5" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="K5" s="23">
         <v>45974.0</v>
       </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="16"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="24"/>
     </row>
     <row r="6">
-      <c r="A6" s="17">
+      <c r="A6" s="7">
         <v>5.0</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="18">
+      <c r="C6" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="I6" s="22"/>
+      <c r="J6" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="K6" s="25">
         <v>45975.0</v>
       </c>
     </row>
     <row r="7" ht="92.25" customHeight="1">
-      <c r="A7" s="14">
+      <c r="A7" s="22">
         <v>6.0</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14" t="s">
+      <c r="B7" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="M7" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="N7" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="O7" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="P7" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="R7" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="S7" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="T7" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="R7" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="T7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
     </row>
     <row r="8">
-      <c r="A8" s="17">
+      <c r="A8" s="7">
         <v>7.0</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17">
+      <c r="B8" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7">
         <v>2.0</v>
       </c>
-      <c r="K8" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="O8" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="P8" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="S8" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="T8" s="21">
+      <c r="K8" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="T8" s="28">
         <v>46000.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="22">
         <v>8.0</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="K9" s="18">
+      <c r="B9" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="K9" s="25">
         <v>45975.0</v>
       </c>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="22">
         <v>9.0</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="K10" s="23">
+      <c r="B10" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="K10" s="30">
         <v>45977.0</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="16"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
     </row>
     <row r="11">
-      <c r="A11" s="14">
+      <c r="A11" s="22">
         <v>10.0</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>128</v>
+      <c r="B11" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="14">
+      <c r="A12" s="22">
         <v>11.0</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>138</v>
+      <c r="B12" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="14">
+      <c r="A13" s="22">
         <v>12.0</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="K13" s="16"/>
+      <c r="B13" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>308</v>
+      </c>
+      <c r="K13" s="24"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="14">
+      <c r="A14" s="22">
         <v>13.0</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="K14" s="16"/>
+      <c r="B14" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="K14" s="24"/>
     </row>
     <row r="15">
-      <c r="A15" s="14">
+      <c r="A15" s="22">
         <v>14.0</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="K15" s="23">
+      <c r="B15" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="K15" s="30">
         <v>45978.0</v>
       </c>
     </row>
     <row r="16" ht="192.0" customHeight="1">
-      <c r="A16" s="14">
+      <c r="A16" s="22">
         <v>15.0</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="K16" s="23">
+      <c r="B16" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="K16" s="30">
         <v>45980.0</v>
       </c>
     </row>
     <row r="17" ht="234.75" customHeight="1">
-      <c r="A17" s="14">
+      <c r="A17" s="22">
         <v>16.0</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="J17" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="K17" s="23">
+      <c r="B17" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>339</v>
+      </c>
+      <c r="K17" s="30">
         <v>45981.0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="14">
+      <c r="A18" s="22">
         <v>17.0</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="K18" s="23">
+      <c r="B18" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="K18" s="30">
         <v>45981.0</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="14">
+      <c r="A19" s="22">
         <v>18.0</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="K19" s="23">
+      <c r="B19" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>354</v>
+      </c>
+      <c r="K19" s="30">
         <v>45981.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14">
+      <c r="A20" s="22">
         <v>19.0</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="K20" s="23">
+      <c r="B20" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="I20" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>362</v>
+      </c>
+      <c r="K20" s="30">
         <v>45981.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="25" t="s">
-        <v>200</v>
+      <c r="A21" s="32" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="22" ht="135.75" customHeight="1">
-      <c r="A22" s="14">
+      <c r="A22" s="22">
         <v>20.0</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="K22" s="26">
+      <c r="B22" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="J22" s="26" t="s">
+        <v>370</v>
+      </c>
+      <c r="K22" s="33">
         <v>46000.0</v>
       </c>
     </row>
     <row r="23" ht="219.0" customHeight="1">
-      <c r="A23" s="14">
+      <c r="A23" s="22">
         <v>21.0</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="K23" s="26">
+      <c r="B23" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="J23" s="26" t="s">
+        <v>371</v>
+      </c>
+      <c r="K23" s="33">
         <v>46000.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="17">
+      <c r="A24" s="7">
         <v>22.0</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="J24" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="K24" s="26">
+      <c r="B24" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="K24" s="33">
         <v>46000.0</v>
       </c>
-      <c r="L24" s="16"/>
+      <c r="L24" s="24"/>
     </row>
     <row r="25" ht="221.25" customHeight="1">
-      <c r="A25" s="17">
+      <c r="A25" s="7">
         <v>24.0</v>
       </c>
-      <c r="B25" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="K25" s="26">
+      <c r="B25" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="J25" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="K25" s="33">
         <v>46000.0</v>
       </c>
-      <c r="L25" s="17" t="s">
-        <v>221</v>
+      <c r="L25" s="7" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="26" ht="199.5" customHeight="1">
-      <c r="A26" s="17">
+      <c r="A26" s="7">
         <v>25.0</v>
       </c>
-      <c r="B26" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="K26" s="26">
+      <c r="B26" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="K26" s="33">
         <v>46001.0</v>
       </c>
     </row>
     <row r="27" ht="147.0" customHeight="1">
-      <c r="A27" s="14">
+      <c r="A27" s="22">
         <v>26.0</v>
       </c>
-      <c r="B27" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="K27" s="26">
+      <c r="B27" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="K27" s="33">
         <v>46002.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14">
+      <c r="A28" s="22">
         <v>27.0</v>
       </c>
-      <c r="B28" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="K28" s="26">
+      <c r="B28" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="J28" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="K28" s="33">
         <v>46003.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14">
+      <c r="A29" s="22">
         <v>28.0</v>
       </c>
-      <c r="B29" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="K29" s="26">
+      <c r="B29" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="J29" s="26" t="s">
+        <v>409</v>
+      </c>
+      <c r="K29" s="33">
         <v>46004.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="14">
+      <c r="A30" s="22">
         <v>29.0</v>
       </c>
-      <c r="B30" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="K30" s="26">
+      <c r="B30" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="I30" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="K30" s="33">
         <v>46006.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="14">
+      <c r="A31" s="22">
         <v>30.0</v>
       </c>
-      <c r="B31" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="K31" s="26">
+      <c r="B31" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="K31" s="33">
         <v>46006.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="B33" s="26"/>
-      <c r="C33" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="K33" s="26">
+      <c r="B33" s="33"/>
+      <c r="C33" s="22" t="s">
+        <v>422</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>423</v>
+      </c>
+      <c r="E33" s="24"/>
+      <c r="F33" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="J33" s="26" t="s">
+        <v>426</v>
+      </c>
+      <c r="K33" s="33">
         <v>45698.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="B34" s="16"/>
-      <c r="C34" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="K34" s="26">
+      <c r="B34" s="24"/>
+      <c r="C34" s="22" t="s">
+        <v>422</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>427</v>
+      </c>
+      <c r="E34" s="24"/>
+      <c r="F34" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="J34" s="26" t="s">
+        <v>429</v>
+      </c>
+      <c r="K34" s="33">
         <v>45700.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="29"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
     </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
@@ -10533,190 +11985,190 @@
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="36"/>
+      <c r="K43" s="36"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="24"/>
+      <c r="K44" s="24"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="24"/>
+      <c r="K45" s="24"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="16"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="24"/>
+      <c r="K46" s="24"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="16"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="16"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
+      <c r="A49" s="24"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="16"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
+      <c r="A50" s="24"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="16"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="16"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="16"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
+      <c r="A53" s="24"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="24"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="16"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
+      <c r="A54" s="24"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="16"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
+      <c r="A55" s="24"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="24"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="16"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="16"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
+      <c r="A56" s="24"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="24"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="16"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
+      <c r="A57" s="24"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
     </row>
     <row r="58" ht="15.75" customHeight="1"/>
     <row r="59" ht="15.75" customHeight="1"/>
@@ -10740,27 +12192,27 @@
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="31"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
+      <c r="A79" s="37"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>269</v>
+      <c r="A80" s="38" t="s">
+        <v>430</v>
+      </c>
+      <c r="B80" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="C80" s="26" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
+      <c r="A81" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="B81" s="24"/>
+      <c r="C81" s="24"/>
     </row>
     <row r="82" ht="15.75" customHeight="1"/>
     <row r="83" ht="15.75" customHeight="1"/>
@@ -11736,7 +13188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -11756,242 +13208,246 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>273</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>274</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>275</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="M1" s="16"/>
+      <c r="L1" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25" t="s">
-        <v>281</v>
-      </c>
-      <c r="M2" s="33"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32" t="s">
+        <v>434</v>
+      </c>
+      <c r="M2" s="39"/>
     </row>
     <row r="3">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34" t="s">
-        <v>282</v>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26">
+      <c r="A4" s="33">
         <v>46007.0</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="M4" s="19" t="s">
-        <v>294</v>
+      <c r="B4" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>438</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>444</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34" t="s">
-        <v>295</v>
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26">
+      <c r="A6" s="33">
         <v>46007.0</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>305</v>
+      <c r="B6" s="26" t="s">
+        <v>449</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34" t="s">
-        <v>306</v>
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26">
+      <c r="A8" s="33">
         <v>46007.0</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>315</v>
+      <c r="B8" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="s">
-        <v>316</v>
+      <c r="A9" s="40" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26">
+      <c r="A10" s="33">
         <v>46007.0</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="M10" s="19" t="s">
-        <v>325</v>
+      <c r="B10" s="26" t="s">
+        <v>449</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21">
+      <c r="A12" s="28">
         <v>45698.0</v>
       </c>
     </row>
@@ -12017,7 +13473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -12033,306 +13489,306 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35"/>
-      <c r="E1" s="36"/>
+      <c r="A1" s="41"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2">
-      <c r="A2" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="F2" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="G2" s="38" t="s">
-        <v>331</v>
+      <c r="A2" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>483</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="s">
-        <v>332</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="C3" s="39" t="s">
-        <v>334</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>335</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>336</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>338</v>
+      <c r="A3" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>486</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>489</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>340</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>335</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="F4" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>344</v>
+      <c r="A4" s="44" t="s">
+        <v>492</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>493</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>494</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>495</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>496</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="s">
-        <v>345</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>346</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>347</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>335</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>348</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>349</v>
-      </c>
-      <c r="G5" s="41" t="s">
-        <v>350</v>
+      <c r="A5" s="44" t="s">
+        <v>498</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>499</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>500</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>501</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>502</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="s">
-        <v>351</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>352</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>353</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>354</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>355</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>356</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>357</v>
+      <c r="A6" s="44" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>507</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>508</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>509</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="s">
-        <v>358</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>359</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>360</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>354</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>362</v>
-      </c>
-      <c r="G7" s="41" t="s">
-        <v>363</v>
+      <c r="A7" s="44" t="s">
+        <v>511</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>512</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>513</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>507</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>514</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="s">
-        <v>364</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>365</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>366</v>
-      </c>
-      <c r="D8" s="40" t="s">
-        <v>367</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>368</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>369</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>370</v>
+      <c r="A8" s="45" t="s">
+        <v>517</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>520</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>521</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>522</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>373</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>374</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="G9" s="41" t="s">
-        <v>377</v>
+      <c r="A9" s="45" t="s">
+        <v>524</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>525</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>526</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>527</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>528</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>529</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>379</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>381</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>382</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>383</v>
-      </c>
-      <c r="G10" s="40" t="s">
-        <v>384</v>
+      <c r="A10" s="44" t="s">
+        <v>531</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>532</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>533</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>534</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>535</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>536</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="s">
-        <v>371</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>387</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>388</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>389</v>
-      </c>
-      <c r="G11" s="41" t="s">
-        <v>390</v>
+      <c r="A11" s="44" t="s">
+        <v>524</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>538</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>539</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>540</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>541</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>542</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>392</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>393</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>394</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>395</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>396</v>
-      </c>
-      <c r="G12" s="41" t="s">
-        <v>397</v>
+      <c r="A12" s="44" t="s">
+        <v>544</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>547</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>548</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>549</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="s">
-        <v>398</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>399</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>401</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="G13" s="41" t="s">
-        <v>403</v>
+      <c r="A13" s="44" t="s">
+        <v>551</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>552</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>553</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>488</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>554</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>555</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="s">
-        <v>404</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>405</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>406</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>407</v>
-      </c>
-      <c r="F14" s="40" t="s">
-        <v>408</v>
-      </c>
-      <c r="G14" s="41" t="s">
-        <v>409</v>
+      <c r="A14" s="45" t="s">
+        <v>557</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>558</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>559</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>488</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>560</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>561</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -12343,7 +13799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -12354,235 +13810,235 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="s">
-        <v>410</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>411</v>
+      <c r="A1" s="47" t="s">
+        <v>563</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="s">
-        <v>412</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>413</v>
+      <c r="A2" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="43" t="s">
-        <v>414</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>415</v>
+      <c r="A3" s="48" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="s">
-        <v>416</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>417</v>
+      <c r="A4" s="48" t="s">
+        <v>569</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="s">
-        <v>418</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>419</v>
+      <c r="A5" s="48" t="s">
+        <v>571</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="s">
-        <v>420</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>421</v>
+      <c r="A6" s="48" t="s">
+        <v>573</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="s">
-        <v>422</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>423</v>
+      <c r="A7" s="48" t="s">
+        <v>575</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="s">
-        <v>403</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>424</v>
+      <c r="A8" s="48" t="s">
+        <v>556</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="s">
-        <v>425</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>426</v>
+      <c r="A9" s="48" t="s">
+        <v>578</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="s">
-        <v>427</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>428</v>
+      <c r="A10" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="s">
-        <v>429</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>58</v>
+      <c r="A11" s="48" t="s">
+        <v>582</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="s">
-        <v>430</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>431</v>
+      <c r="A12" s="48" t="s">
+        <v>583</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="s">
-        <v>432</v>
-      </c>
-      <c r="B13" s="42" t="s">
-        <v>433</v>
+      <c r="A13" s="48" t="s">
+        <v>585</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="s">
-        <v>434</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>431</v>
+      <c r="A14" s="48" t="s">
+        <v>587</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="s">
-        <v>435</v>
-      </c>
-      <c r="B15" s="42" t="s">
-        <v>436</v>
+      <c r="A15" s="48" t="s">
+        <v>588</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="s">
-        <v>437</v>
-      </c>
-      <c r="B16" s="42" t="s">
-        <v>438</v>
+      <c r="A16" s="48" t="s">
+        <v>590</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="B17" s="42" t="s">
-        <v>440</v>
+      <c r="A17" s="48" t="s">
+        <v>592</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="s">
-        <v>441</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>442</v>
+      <c r="A18" s="48" t="s">
+        <v>594</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="s">
-        <v>443</v>
-      </c>
-      <c r="B19" s="42" t="s">
-        <v>444</v>
+      <c r="A19" s="48" t="s">
+        <v>596</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="s">
-        <v>397</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>445</v>
+      <c r="A20" s="48" t="s">
+        <v>550</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="s">
-        <v>446</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>445</v>
+      <c r="A21" s="48" t="s">
+        <v>599</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="s">
-        <v>447</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>444</v>
+      <c r="A22" s="48" t="s">
+        <v>600</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="s">
-        <v>448</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>449</v>
+      <c r="A23" s="48" t="s">
+        <v>601</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="s">
-        <v>450</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>451</v>
+      <c r="A24" s="48" t="s">
+        <v>603</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="s">
-        <v>452</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>451</v>
+      <c r="A25" s="48" t="s">
+        <v>605</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="s">
-        <v>453</v>
-      </c>
-      <c r="B26" s="42" t="s">
-        <v>191</v>
+      <c r="A26" s="48" t="s">
+        <v>606</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="s">
-        <v>454</v>
-      </c>
-      <c r="B27" s="42" t="s">
-        <v>184</v>
+      <c r="A27" s="48" t="s">
+        <v>607</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="s">
-        <v>455</v>
-      </c>
-      <c r="B28" s="42" t="s">
-        <v>207</v>
+      <c r="A28" s="48" t="s">
+        <v>608</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="s">
-        <v>456</v>
-      </c>
-      <c r="B29" s="42" t="s">
-        <v>457</v>
+      <c r="A29" s="48" t="s">
+        <v>609</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>610</v>
       </c>
     </row>
   </sheetData>
